--- a/product_selector_out/STM8S207-208.xlsx
+++ b/product_selector_out/STM8S207-208.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG30"/>
+  <dimension ref="A1:AH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,8 @@
     <col width="23.46484375" customWidth="1" min="30" max="30"/>
     <col width="11.6328125" customWidth="1" min="31" max="31"/>
     <col width="43.6484375" customWidth="1" min="32" max="32"/>
-    <col width="52" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="52" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -710,6 +711,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -877,6 +883,11 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -1044,6 +1055,11 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -1211,6 +1227,11 @@
       </c>
       <c r="AG13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -1378,6 +1399,11 @@
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -1545,6 +1571,11 @@
       </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -1712,6 +1743,11 @@
       </c>
       <c r="AG16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -1879,6 +1915,11 @@
       </c>
       <c r="AG17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -2046,6 +2087,11 @@
       </c>
       <c r="AG18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -2213,6 +2259,11 @@
       </c>
       <c r="AG19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -2380,6 +2431,11 @@
       </c>
       <c r="AG20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -2547,6 +2603,11 @@
       </c>
       <c r="AG21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -2714,6 +2775,11 @@
       </c>
       <c r="AG22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -2881,6 +2947,11 @@
       </c>
       <c r="AG23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -3048,6 +3119,11 @@
       </c>
       <c r="AG24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -3215,6 +3291,11 @@
       </c>
       <c r="AG25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -3382,6 +3463,11 @@
       </c>
       <c r="AG26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -3549,6 +3635,11 @@
       </c>
       <c r="AG27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -3716,6 +3807,11 @@
       </c>
       <c r="AG28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -3883,6 +3979,11 @@
       </c>
       <c r="AG29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -4050,14 +4151,19 @@
       </c>
       <c r="AG30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
@@ -4092,7 +4198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG30"/>
+  <dimension ref="A1:AH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4128,6 +4234,7 @@
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
     <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4314,6 +4421,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -4479,7 +4591,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG11" s="6" t="inlineStr">
+      <c r="AG11" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4646,7 +4763,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG12" s="6" t="inlineStr">
+      <c r="AG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4813,7 +4935,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG13" s="6" t="inlineStr">
+      <c r="AG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4980,7 +5107,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG14" s="6" t="inlineStr">
+      <c r="AG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5147,7 +5279,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG15" s="6" t="inlineStr">
+      <c r="AG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5314,7 +5451,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG16" s="6" t="inlineStr">
+      <c r="AG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5481,7 +5623,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="6" t="inlineStr">
+      <c r="AG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5648,7 +5795,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="6" t="inlineStr">
+      <c r="AG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5815,7 +5967,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="6" t="inlineStr">
+      <c r="AG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5982,7 +6139,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG20" s="6" t="inlineStr">
+      <c r="AG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6149,7 +6311,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG21" s="6" t="inlineStr">
+      <c r="AG21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6316,7 +6483,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG22" s="6" t="inlineStr">
+      <c r="AG22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6483,7 +6655,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG23" s="6" t="inlineStr">
+      <c r="AG23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6650,7 +6827,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG24" s="6" t="inlineStr">
+      <c r="AG24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6817,7 +6999,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG25" s="6" t="inlineStr">
+      <c r="AG25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6984,7 +7171,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG26" s="6" t="inlineStr">
+      <c r="AG26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7151,7 +7343,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG27" s="6" t="inlineStr">
+      <c r="AG27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7318,7 +7515,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG28" s="6" t="inlineStr">
+      <c r="AG28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7485,7 +7687,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG29" s="6" t="inlineStr">
+      <c r="AG29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7652,7 +7859,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG30" s="6" t="inlineStr">
+      <c r="AG30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7660,8 +7872,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
